--- a/output/retail_report_log.xlsx
+++ b/output/retail_report_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,6 +533,40 @@
         <v>7</v>
       </c>
       <c r="J3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" t="n">
+        <v>222</v>
+      </c>
+      <c r="D4" t="n">
+        <v>128</v>
+      </c>
+      <c r="E4" t="n">
+        <v>94</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>114</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="n">
         <v>6</v>
       </c>
     </row>

--- a/output/retail_report_log.xlsx
+++ b/output/retail_report_log.xlsx
@@ -539,35 +539,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D4" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/retail_report_log.xlsx
+++ b/output/retail_report_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,176 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" t="n">
+        <v>224</v>
+      </c>
+      <c r="D5" t="n">
+        <v>105</v>
+      </c>
+      <c r="E5" t="n">
+        <v>119</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>73</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>21</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>23</v>
+      </c>
+      <c r="C6" t="n">
+        <v>224</v>
+      </c>
+      <c r="D6" t="n">
+        <v>88</v>
+      </c>
+      <c r="E6" t="n">
+        <v>136</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>48</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>23</v>
+      </c>
+      <c r="C7" t="n">
+        <v>224</v>
+      </c>
+      <c r="D7" t="n">
+        <v>88</v>
+      </c>
+      <c r="E7" t="n">
+        <v>136</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>48</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J7" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>32</v>
+      </c>
+      <c r="C8" t="n">
+        <v>215</v>
+      </c>
+      <c r="D8" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" t="n">
+        <v>155</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>17</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>33</v>
+      </c>
+      <c r="C9" t="n">
+        <v>214</v>
+      </c>
+      <c r="D9" t="n">
+        <v>49</v>
+      </c>
+      <c r="E9" t="n">
+        <v>165</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/retail_report_log.xlsx
+++ b/output/retail_report_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -740,6 +740,40 @@
         <v>43</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-232</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>36</v>
+      </c>
+      <c r="C10" t="n">
+        <v>218</v>
+      </c>
+      <c r="D10" t="n">
+        <v>52</v>
+      </c>
+      <c r="E10" t="n">
+        <v>166</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
